--- a/p6_deployment/data/germany/data_preparation/df_selected.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_selected.xlsx
@@ -425,166 +425,241 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG28"/>
+  <dimension ref="A1:AV28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_team_away</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>h2h_35_segun_loc</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_35</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>h2h_3_segun_loc</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>h2h_3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_match_mean_rat_player_start_home_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>is_rival_match</t>
         </is>
@@ -593,24 +668,30 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.580945349104867</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C2" t="n">
-        <v>2.256653079297977</v>
+        <v>0.741870753747244</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4544050538957611</v>
+        <v>-0.754493963767528</v>
       </c>
       <c r="E2" t="n">
-        <v>3.133458207594984</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+        <v>1.97876599698247</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.1972197334419516</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.806475834200292</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -635,36 +716,51 @@
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.127994619003312</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C3" t="n">
-        <v>2.256653079297977</v>
+        <v>1.323977300355787</v>
       </c>
       <c r="D3" t="n">
-        <v>2.074538358259747</v>
+        <v>1.541912804490791</v>
       </c>
       <c r="E3" t="n">
-        <v>3.133458207594984</v>
+        <v>1.97876599698247</v>
       </c>
       <c r="F3" t="n">
-        <v>0.212721161331109</v>
+        <v>0.3695891883107441</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4903481272080951</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H3" t="n">
-        <v>0.465572143691882</v>
+        <v>4.806475834200292</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -690,37 +786,64 @@
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.7970459839282976</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C4" t="n">
-        <v>2.256653079297977</v>
+        <v>1.716266494809371</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1936482678498333</v>
+        <v>1.104501991489206</v>
       </c>
       <c r="E4" t="n">
-        <v>3.133458207594984</v>
+        <v>1.97876599698247</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6395162417760367</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+        <v>1.786611492692483</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.001490810544533536</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6089044548017132</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.5272045276949199</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5386005136997623</v>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -741,8 +864,23 @@
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="5">
@@ -752,20 +890,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1176198887759649</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C5" t="n">
-        <v>2.256653079297977</v>
+        <v>0.2610001282880125</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.378806359777146</v>
+        <v>-0.09837774426515113</v>
       </c>
       <c r="E5" t="n">
-        <v>3.133458207594984</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+        <v>1.97876599698247</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.3591651396570075</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.806475834200292</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -790,33 +934,58 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.6838083014029088</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C6" t="n">
-        <v>2.256653079297977</v>
+        <v>0.1091462465640447</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.829211413207762</v>
+        <v>0.1567785633191066</v>
       </c>
       <c r="E6" t="n">
-        <v>3.133458207594984</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+        <v>1.97876599698247</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.003875362653046</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.9435076852138952</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.574342265380581</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -839,33 +1008,52 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1466013704499423</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C7" t="n">
-        <v>2.256653079297977</v>
+        <v>1.437867711648763</v>
       </c>
       <c r="D7" t="n">
-        <v>1.179607580611069</v>
+        <v>-0.6451412605171318</v>
       </c>
       <c r="E7" t="n">
-        <v>3.133458207594984</v>
+        <v>1.97876599698247</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.150858683640324</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+        <v>-1.627737488341612</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.806475834200292</v>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -890,33 +1078,52 @@
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.136759031504464</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1107601919845012</v>
+        <v>1.804847925815019</v>
       </c>
       <c r="D8" t="n">
-        <v>2.074538358259747</v>
+        <v>-1.191904776769113</v>
       </c>
       <c r="E8" t="n">
-        <v>3.133458207594984</v>
+        <v>1.97876599698247</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2986212805331784</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+        <v>-0.1972197334419516</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.806475834200292</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -941,35 +1148,64 @@
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.249996714029853</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C9" t="n">
-        <v>2.256653079297977</v>
+        <v>-0.4729603000444986</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1936482678498333</v>
+        <v>-1.410610183269905</v>
       </c>
       <c r="E9" t="n">
-        <v>3.133458207594984</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+        <v>0.09518247181964085</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.570684284405742</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-1.179757309153502</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1.018059785448941</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.2386002405046198</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.4576315517288156</v>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -986,43 +1222,86 @@
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AC9" t="n">
+        <v>-0.5073471214228522</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-1.197068098244505</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.5683113252867548</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.5381528234727851</v>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="n">
+        <v>-0.1461757720354481</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0.175619748448436</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.09070537845287552</v>
+      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>-0.1349534906294526</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.332670352041344</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-0.09140010953732815</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-0.6776083718822182</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-0.6903351341630821</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.47647207908063</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1345123541393592</v>
+        <v>0.1344552268513727</v>
       </c>
       <c r="D10" t="n">
-        <v>1.827660902356663</v>
+        <v>-1.082552073518716</v>
       </c>
       <c r="E10" t="n">
-        <v>3.133458207594984</v>
+        <v>-0.1214296335740845</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.662201125504612</v>
+        <v>1.786611492692483</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.849583076661939</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.370864502294484</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.4710084373346808</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1651869347333529</v>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -1036,29 +1315,32 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
-      <c r="X10" t="n">
-        <v>-0.5239124094119472</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-0.5336512952030967</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-0.5501919728676752</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.369901346229692</v>
-      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="n">
-        <v>-0.2154898269961419</v>
-      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="n">
-        <v>-0.5576836106671057</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="11">
@@ -1068,20 +1350,26 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6372979947266271</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C11" t="n">
-        <v>2.256653079297977</v>
+        <v>0.08383726627671673</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.613193639292564</v>
+        <v>0.6306402774041565</v>
       </c>
       <c r="E11" t="n">
-        <v>3.133458207594984</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+        <v>1.97876599698247</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.438801181090714</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.806475834200292</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1106,8 +1394,23 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="12">
@@ -1117,24 +1420,32 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-1.363234396555242</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C12" t="n">
-        <v>1.734115915816709</v>
+        <v>0.5267444213049562</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4544050538957611</v>
+        <v>-1.301257480019509</v>
       </c>
       <c r="E12" t="n">
-        <v>3.133458207594984</v>
+        <v>1.507870115691762</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2986212805331784</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+        <v>0.3695891883107441</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.4710084373346808</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.1651869347333529</v>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1157,8 +1468,23 @@
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="13">
@@ -1168,30 +1494,38 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9392651481276638</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.635715587450242</v>
+        <v>-1.358774610100978</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3942362007710887</v>
+        <v>0.9222474860718796</v>
       </c>
       <c r="E13" t="n">
-        <v>4.855600117935343</v>
+        <v>-1.468191854065507</v>
       </c>
       <c r="F13" t="n">
-        <v>4.133013215623979</v>
+        <v>-0.3726605901749289</v>
       </c>
       <c r="G13" t="n">
-        <v>2.500244933013146</v>
+        <v>4.256064548547412</v>
       </c>
       <c r="H13" t="n">
-        <v>1.720227112671431</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.781484793578249</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.010738775325809</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.058814064093999</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.032948611842629</v>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1203,56 +1537,97 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="n">
-        <v>1.099518085418156</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.590566165167378</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>-0.4839789641794126</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.6377662360768745</v>
-      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>-0.3099450631083298</v>
+      </c>
       <c r="AD13" t="n">
-        <v>0.003268937196141936</v>
-      </c>
-      <c r="AE13" t="inlineStr"/>
+        <v>1.310762565176785</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.643559142272541</v>
+      </c>
       <c r="AF13" t="n">
-        <v>0.7797032608578869</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>-0.2192196608739769</v>
+        <v>0.8647720645904772</v>
+      </c>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="n">
+        <v>2.513570602589012</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-0.1093831578336911</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0.1392004599075714</v>
+      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="n">
+        <v>1.138653336171462</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.6613509479025669</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.137815933552238</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.826747612047694</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.363665937986686</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9770110423027935</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C14" t="n">
-        <v>2.256653079297977</v>
+        <v>1.235395869350139</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.378806359777146</v>
+        <v>0.5212875741537604</v>
       </c>
       <c r="E14" t="n">
-        <v>3.133458207594984</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+        <v>1.97876599698247</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.9934513139993099</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.2347588133950737</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4609986147789265</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.9557475844431046</v>
+      </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1273,31 +1648,52 @@
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.400980290730371</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C15" t="n">
-        <v>2.256653079297977</v>
+        <v>1.804847925815019</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.104008886492454</v>
+        <v>0.9586983871553449</v>
       </c>
       <c r="E15" t="n">
-        <v>3.133458207594984</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+        <v>1.97876599698247</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.3591651396570075</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.806475834200292</v>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1322,36 +1718,51 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5240603122012383</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C16" t="n">
-        <v>2.256653079297977</v>
+        <v>0.7545252438909079</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.104008886492454</v>
+        <v>-1.337708381102974</v>
       </c>
       <c r="E16" t="n">
-        <v>3.133458207594984</v>
+        <v>1.97876599698247</v>
       </c>
       <c r="F16" t="n">
-        <v>0.04227368070967985</v>
+        <v>-0.9934513139993099</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.519548678596956</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7890828252876672</v>
+        <v>4.806475834200292</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -1377,33 +1788,58 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.354469984054089</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C17" t="n">
-        <v>2.256653079297977</v>
+        <v>-0.2198704971712189</v>
       </c>
       <c r="D17" t="n">
-        <v>1.117888216635298</v>
+        <v>-1.483511985436836</v>
       </c>
       <c r="E17" t="n">
-        <v>3.133458207594984</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+        <v>1.97876599698247</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.543693383369899</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.707258061274288</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.1306247453122206</v>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
@@ -1426,33 +1862,52 @@
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.090248724828182</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C18" t="n">
-        <v>2.256653079297977</v>
+        <v>-0.194561516883891</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9018704427201001</v>
+        <v>1.323207397989999</v>
       </c>
       <c r="E18" t="n">
-        <v>3.133458207594984</v>
+        <v>1.97876599698247</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.321306164261753</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+        <v>0.9498935605813611</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.806475834200292</v>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1477,35 +1932,58 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.55196386743089</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C19" t="n">
-        <v>2.256653079297977</v>
+        <v>1.121505458057164</v>
       </c>
       <c r="D19" t="n">
-        <v>1.796801220368778</v>
+        <v>1.068051090405741</v>
       </c>
       <c r="E19" t="n">
-        <v>3.133458207594984</v>
+        <v>1.97876599698247</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6395162417760367</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+        <v>0.7609572533304625</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.9435076852138952</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.7222481054033678</v>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
@@ -1528,36 +2006,51 @@
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6750438889017567</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C20" t="n">
-        <v>1.158258633612863</v>
+        <v>-0.8019770437797622</v>
       </c>
       <c r="D20" t="n">
-        <v>1.117888216635298</v>
+        <v>-0.3899849529328742</v>
       </c>
       <c r="E20" t="n">
-        <v>3.133458207594984</v>
+        <v>1.97876599698247</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4690687611546076</v>
+        <v>1.260288922493552</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.849583076661939</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.370864502294484</v>
+        <v>4.806475834200292</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -1574,56 +2067,73 @@
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
-      <c r="X20" t="n">
-        <v>-1.670424621989281</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>-1.507467294177631</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0.514615788485408</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>-0.8785658287791878</v>
-      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="n">
-        <v>0.01759428949813836</v>
-      </c>
+      <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="n">
-        <v>-1.038657077002678</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.4573329363521312</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C21" t="n">
-        <v>2.256653079297977</v>
+        <v>-1.14364827765869</v>
       </c>
       <c r="D21" t="n">
-        <v>1.179607580611069</v>
+        <v>0.6670911784876219</v>
       </c>
       <c r="E21" t="n">
-        <v>3.133458207594984</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+        <v>0.9993025638977986</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9498935605813611</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.2347588133950737</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.01728109471056615</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.4576315517288156</v>
+      </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1640,35 +2150,80 @@
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AC21" t="n">
+        <v>0.4987763484521802</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-1.541215809428621</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-1.796382588256907</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-1.199043734333473</v>
+      </c>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="n">
+        <v>-0.7594485677246998</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>-0.1228330507583776</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.09010594418816957</v>
+      </c>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="n">
+        <v>-1.282063465671144</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>-0.9951925175473821</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>-0.9670505483314656</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>-1.796676474116915</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>-2.071352985194133</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.4195870421770016</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C22" t="n">
-        <v>2.256653079297977</v>
+        <v>0.9443425960458677</v>
       </c>
       <c r="D22" t="n">
-        <v>1.472774559495981</v>
+        <v>-0.4264358540163395</v>
       </c>
       <c r="E22" t="n">
-        <v>3.133458207594984</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+        <v>1.97876599698247</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.003875362653046</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4.806475834200292</v>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1693,8 +2248,23 @@
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="23">
@@ -1704,20 +2274,26 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-1.023521348979075</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C23" t="n">
-        <v>2.256653079297977</v>
+        <v>0.2989635987190045</v>
       </c>
       <c r="D23" t="n">
-        <v>1.796801220368778</v>
+        <v>-0.9731993702683203</v>
       </c>
       <c r="E23" t="n">
-        <v>3.133458207594984</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+        <v>1.97876599698247</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.543693383369899</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.806475834200292</v>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1742,8 +2318,23 @@
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="24">
@@ -1753,24 +2344,32 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.212250819854723</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C24" t="n">
-        <v>2.256653079297977</v>
+        <v>1.602376083516395</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3942362007710887</v>
+        <v>-1.155453875685647</v>
       </c>
       <c r="E24" t="n">
-        <v>3.133458207594984</v>
+        <v>1.97876599698247</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.980411203018895</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+        <v>-0.3726605901749289</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.9435076852138952</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.4264364253577941</v>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
@@ -1793,8 +2392,23 @@
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="25">
@@ -1804,24 +2418,32 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.052502830653053</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C25" t="n">
-        <v>2.256653079297977</v>
+        <v>1.450522201792427</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.9651403175469695</v>
+        <v>1.031600189322276</v>
       </c>
       <c r="E25" t="n">
-        <v>3.133458207594984</v>
+        <v>1.97876599698247</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8099637223974658</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+        <v>-0.8719922593380179</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.707258061274288</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.2785305853350074</v>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -1844,8 +2466,23 @@
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="26">
@@ -1855,20 +2492,26 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.6460624072277792</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C26" t="n">
-        <v>2.256653079297977</v>
+        <v>0.4128540100119804</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.101069221886177</v>
+        <v>-0.6086903594336665</v>
       </c>
       <c r="E26" t="n">
-        <v>3.133458207594984</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+        <v>1.97876599698247</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.1162470303344236</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.806475834200292</v>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1893,8 +2536,23 @@
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="27">
@@ -1904,24 +2562,32 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.7215541955780383</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1107601919845012</v>
+        <v>-0.2325249873148829</v>
       </c>
       <c r="D27" t="n">
-        <v>1.889380266332434</v>
+        <v>-0.6815921616005972</v>
       </c>
       <c r="E27" t="n">
-        <v>3.133458207594984</v>
+        <v>-0.1214296335740845</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.150858683640324</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+        <v>1.624666086477427</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.9435076852138952</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.574342265380581</v>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
@@ -1935,29 +2601,56 @@
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
-      <c r="X27" t="n">
-        <v>-1.455506028246147</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>-1.575105791941537</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>-0.5333826439555972</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.08227833917012767</v>
-      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
+      <c r="AC27" t="n">
+        <v>-0.6242131872992813</v>
+      </c>
       <c r="AD27" t="n">
-        <v>1.031626818735806</v>
-      </c>
-      <c r="AE27" t="inlineStr"/>
+        <v>-2.064364143242678</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>-1.910098268084225</v>
+      </c>
       <c r="AF27" t="n">
-        <v>-1.078920355615719</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>4.561634645420201</v>
+        <v>-1.264846255712045</v>
+      </c>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="n">
+        <v>-0.5477829130492949</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.9779613287497709</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>-0.2651075775822376</v>
+      </c>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="n">
+        <v>-1.067482418707855</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0.01953090607690237</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>-0.6735016759804702</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>-1.982205839389495</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>-1.80700155704934</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>5.308540478011726</v>
       </c>
     </row>
     <row r="28">
@@ -1967,24 +2660,32 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7127897830768862</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C28" t="n">
-        <v>2.256653079297977</v>
+        <v>1.058233007338844</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.9651403175469695</v>
+        <v>0.7035420795710873</v>
       </c>
       <c r="E28" t="n">
-        <v>3.133458207594984</v>
+        <v>1.97876599698247</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.6395162417760367</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+        <v>-0.8719922593380179</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.707258061274288</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0.1306247453122206</v>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
@@ -2007,8 +2708,23 @@
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="n">
-        <v>-0.2192196608739769</v>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/germany/data_preparation/df_selected.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV28"/>
+  <dimension ref="A1:AV32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,23 +668,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C2" t="n">
-        <v>0.741870753747244</v>
+        <v>-0.09332559573457906</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.754493963767528</v>
+        <v>-1.046101172435251</v>
       </c>
       <c r="E2" t="n">
-        <v>1.97876599698247</v>
+        <v>-1.468191854065507</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1972197334419516</v>
+        <v>1.260288922493552</v>
       </c>
       <c r="G2" t="n">
         <v>2.532501625081374</v>
@@ -692,8 +692,12 @@
       <c r="H2" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>-0.9435076852138952</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.574342265380581</v>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -712,25 +716,49 @@
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>0.5520993014240805</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-2.439451353851685</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-1.439532727683684</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-1.271491883433217</v>
+      </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>-1.360535888978865</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.6725182416976619</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-0.05387862646966592</v>
+      </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>-1.072308374290293</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.8629730943203149</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-0.9461446075191189</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-2.087185343268945</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-2.29405840323754</v>
+      </c>
       <c r="AV2" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -738,23 +766,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C3" t="n">
-        <v>1.323977300355787</v>
+        <v>-1.232229708664338</v>
       </c>
       <c r="D3" t="n">
-        <v>1.541912804490791</v>
+        <v>-0.5722394583502011</v>
       </c>
       <c r="E3" t="n">
-        <v>1.97876599698247</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3695891883107441</v>
+        <v>1.786611492692483</v>
       </c>
       <c r="G3" t="n">
         <v>2.532501625081374</v>
@@ -762,10 +790,18 @@
       <c r="H3" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>-0.4710084373346808</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.4264364253577941</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.4576315517288156</v>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -808,23 +844,23 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.607676405679417</v>
+        <v>1.643079247984667</v>
       </c>
       <c r="C4" t="n">
-        <v>1.716266494809371</v>
+        <v>0.3369270691499964</v>
       </c>
       <c r="D4" t="n">
-        <v>1.104501991489206</v>
+        <v>0.2661312665695027</v>
       </c>
       <c r="E4" t="n">
-        <v>1.97876599698247</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F4" t="n">
-        <v>1.786611492692483</v>
+        <v>-0.4806241943182994</v>
       </c>
       <c r="G4" t="n">
         <v>2.532501625081374</v>
@@ -832,18 +868,10 @@
       <c r="H4" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.001490810544533536</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.6089044548017132</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.5272045276949199</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.5386005136997623</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -886,23 +914,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2610001282880125</v>
+        <v>1.197432398919147</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.09837774426515113</v>
+        <v>1.177403793656137</v>
       </c>
       <c r="E5" t="n">
-        <v>1.97876599698247</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3591651396570075</v>
+        <v>1.624666086477427</v>
       </c>
       <c r="G5" t="n">
         <v>2.532501625081374</v>
@@ -956,23 +984,23 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.572273563374167</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1091462465640447</v>
+        <v>0.741870753747244</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1567785633191066</v>
+        <v>-0.754493963767528</v>
       </c>
       <c r="E6" t="n">
-        <v>1.97876599698247</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F6" t="n">
-        <v>1.003875362653046</v>
+        <v>-0.1972197334419516</v>
       </c>
       <c r="G6" t="n">
         <v>2.532501625081374</v>
@@ -980,12 +1008,8 @@
       <c r="H6" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I6" t="n">
-        <v>-0.9435076852138952</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-0.574342265380581</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -1030,23 +1054,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1.607676405679417</v>
       </c>
       <c r="C7" t="n">
-        <v>1.437867711648763</v>
+        <v>1.716266494809371</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6451412605171318</v>
+        <v>1.104501991489206</v>
       </c>
       <c r="E7" t="n">
-        <v>1.97876599698247</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.627737488341612</v>
+        <v>1.786611492692483</v>
       </c>
       <c r="G7" t="n">
         <v>2.532501625081374</v>
@@ -1054,10 +1078,18 @@
       <c r="H7" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>0.001490810544533536</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6089044548017132</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.5272045276949199</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5386005136997623</v>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -1100,23 +1132,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1.607676405679417</v>
       </c>
       <c r="C8" t="n">
-        <v>1.804847925815019</v>
+        <v>1.323977300355787</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.191904776769113</v>
+        <v>1.541912804490791</v>
       </c>
       <c r="E8" t="n">
-        <v>1.97876599698247</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1972197334419516</v>
+        <v>0.3695891883107441</v>
       </c>
       <c r="G8" t="n">
         <v>2.532501625081374</v>
@@ -1170,23 +1202,23 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1.607676405679417</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.4729603000444986</v>
+        <v>0.1344552268513727</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.410610183269905</v>
+        <v>-1.082552073518716</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09518247181964085</v>
+        <v>-0.1214296335740845</v>
       </c>
       <c r="F9" t="n">
-        <v>1.570684284405742</v>
+        <v>1.786611492692483</v>
       </c>
       <c r="G9" t="n">
         <v>2.532501625081374</v>
@@ -1195,17 +1227,13 @@
         <v>4.806475834200292</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.179757309153502</v>
+        <v>-0.4710084373346808</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.018059785448941</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-0.2386002405046198</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-0.4576315517288156</v>
-      </c>
+        <v>0.1651869347333529</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1222,49 +1250,25 @@
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="n">
-        <v>-0.5073471214228522</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-1.197068098244505</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-0.5683113252867548</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>-0.5381528234727851</v>
-      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="n">
-        <v>-0.1461757720354481</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-0.175619748448436</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.09070537845287552</v>
-      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="n">
-        <v>-0.1349534906294526</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.332670352041344</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-0.09140010953732815</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>-0.6776083718822182</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>-0.6903351341630821</v>
-      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1272,23 +1276,23 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1344552268513727</v>
+        <v>0.1091462465640447</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.082552073518716</v>
+        <v>0.1567785633191066</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1214296335740845</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F10" t="n">
-        <v>1.786611492692483</v>
+        <v>1.003875362653046</v>
       </c>
       <c r="G10" t="n">
         <v>2.532501625081374</v>
@@ -1297,10 +1301,10 @@
         <v>4.806475834200292</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4710084373346808</v>
+        <v>-0.9435076852138952</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1651869347333529</v>
+        <v>-0.574342265380581</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1346,23 +1350,23 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.572273563374167</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C11" t="n">
-        <v>0.08383726627671673</v>
+        <v>1.804847925815019</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6306402774041565</v>
+        <v>-1.191904776769113</v>
       </c>
       <c r="E11" t="n">
-        <v>1.97876599698247</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.438801181090714</v>
+        <v>-0.1972197334419516</v>
       </c>
       <c r="G11" t="n">
         <v>2.532501625081374</v>
@@ -1416,23 +1420,23 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1.607676405679417</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5267444213049562</v>
+        <v>1.437867711648763</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.301257480019509</v>
+        <v>-0.6451412605171318</v>
       </c>
       <c r="E12" t="n">
-        <v>1.507870115691762</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3695891883107441</v>
+        <v>-1.627737488341612</v>
       </c>
       <c r="G12" t="n">
         <v>2.532501625081374</v>
@@ -1440,12 +1444,8 @@
       <c r="H12" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I12" t="n">
-        <v>-0.4710084373346808</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.1651869347333529</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1490,41 +1490,41 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>fcxqFy2l</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.572273563374167</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.358774610100978</v>
+        <v>-0.4729603000444986</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9222474860718796</v>
+        <v>-1.410610183269905</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.468191854065507</v>
+        <v>0.09518247181964085</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3726605901749289</v>
+        <v>1.570684284405742</v>
       </c>
       <c r="G13" t="n">
-        <v>4.256064548547412</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H13" t="n">
         <v>4.806475834200292</v>
       </c>
       <c r="I13" t="n">
-        <v>3.781484793578249</v>
+        <v>-1.179757309153502</v>
       </c>
       <c r="J13" t="n">
-        <v>4.010738775325809</v>
+        <v>-1.018059785448941</v>
       </c>
       <c r="K13" t="n">
-        <v>2.058814064093999</v>
+        <v>-0.2386002405046198</v>
       </c>
       <c r="L13" t="n">
-        <v>2.032948611842629</v>
+        <v>-0.4576315517288156</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1543,27 +1543,27 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>-0.3099450631083298</v>
+        <v>-0.5011058001155981</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.310762565176785</v>
+        <v>-1.223970419192412</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.643559142272541</v>
+        <v>-0.5829300459338373</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.8647720645904772</v>
+        <v>-0.5495033543548912</v>
       </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>2.513570602589012</v>
+        <v>-0.1492061132814932</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.1093831578336911</v>
+        <v>-0.176180405359852</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.1392004599075714</v>
+        <v>0.08829128664772155</v>
       </c>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
@@ -1571,19 +1571,19 @@
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="n">
-        <v>1.138653336171462</v>
+        <v>-0.1220187193975283</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.6613509479025669</v>
+        <v>1.40766527596645</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.137815933552238</v>
+        <v>-0.08870237166363239</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.826747612047694</v>
+        <v>-0.7029146926355367</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.363665937986686</v>
+        <v>-0.6857498272956946</v>
       </c>
       <c r="AV13" t="n">
         <v>-0.1883756946268106</v>
@@ -1592,23 +1592,23 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C14" t="n">
-        <v>1.235395869350139</v>
+        <v>0.2610001282880125</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5212875741537604</v>
+        <v>-0.09837774426515113</v>
       </c>
       <c r="E14" t="n">
-        <v>1.97876599698247</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9934513139993099</v>
+        <v>-0.3591651396570075</v>
       </c>
       <c r="G14" t="n">
         <v>2.532501625081374</v>
@@ -1616,18 +1616,10 @@
       <c r="H14" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I14" t="n">
-        <v>-0.2347588133950737</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.4609986147789265</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-1.004405008704159</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-0.9557475844431046</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1670,23 +1662,23 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.572273563374167</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C15" t="n">
-        <v>1.804847925815019</v>
+        <v>0.5267444213049562</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9586983871553449</v>
+        <v>-1.301257480019509</v>
       </c>
       <c r="E15" t="n">
-        <v>1.97876599698247</v>
+        <v>1.507870115691762</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3591651396570075</v>
+        <v>0.3695891883107441</v>
       </c>
       <c r="G15" t="n">
         <v>2.532501625081374</v>
@@ -1694,8 +1686,12 @@
       <c r="H15" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>-0.4710084373346808</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.1651869347333529</v>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -1740,23 +1736,23 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7545252438909079</v>
+        <v>0.08383726627671673</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.337708381102974</v>
+        <v>0.6306402774041565</v>
       </c>
       <c r="E16" t="n">
-        <v>1.97876599698247</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9934513139993099</v>
+        <v>-1.438801181090714</v>
       </c>
       <c r="G16" t="n">
         <v>2.532501625081374</v>
@@ -1810,38 +1806,42 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>fcxqFy2l</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.2198704971712189</v>
+        <v>-1.358774610100978</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.483511985436836</v>
+        <v>0.9222474860718796</v>
       </c>
       <c r="E17" t="n">
-        <v>1.97876599698247</v>
+        <v>-1.468191854065507</v>
       </c>
       <c r="F17" t="n">
-        <v>1.543693383369899</v>
+        <v>-0.3726605901749289</v>
       </c>
       <c r="G17" t="n">
-        <v>2.532501625081374</v>
+        <v>4.256064548547412</v>
       </c>
       <c r="H17" t="n">
         <v>4.806475834200292</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.707258061274288</v>
+        <v>3.781484793578249</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1306247453122206</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+        <v>4.010738775325809</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.058814064093999</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.032948611842629</v>
+      </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1858,25 +1858,49 @@
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>-0.3099450631083298</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.310762565176785</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.643559142272541</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.8647720645904772</v>
+      </c>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
+      <c r="AI17" t="n">
+        <v>2.513570602589012</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0.1093831578336911</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-0.1392004599075714</v>
+      </c>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="inlineStr"/>
+      <c r="AQ17" t="n">
+        <v>1.138653336171462</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.6613509479025669</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.137815933552238</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.826747612047694</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.363665937986686</v>
+      </c>
       <c r="AV17" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1884,23 +1908,23 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.194561516883891</v>
+        <v>1.804847925815019</v>
       </c>
       <c r="D18" t="n">
-        <v>1.323207397989999</v>
+        <v>0.9586983871553449</v>
       </c>
       <c r="E18" t="n">
-        <v>1.97876599698247</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9498935605813611</v>
+        <v>-0.3591651396570075</v>
       </c>
       <c r="G18" t="n">
         <v>2.532501625081374</v>
@@ -1954,23 +1978,23 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1.607676405679417</v>
       </c>
       <c r="C19" t="n">
-        <v>1.121505458057164</v>
+        <v>1.235395869350139</v>
       </c>
       <c r="D19" t="n">
-        <v>1.068051090405741</v>
+        <v>0.5212875741537604</v>
       </c>
       <c r="E19" t="n">
-        <v>1.97876599698247</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7609572533304625</v>
+        <v>-0.9934513139993099</v>
       </c>
       <c r="G19" t="n">
         <v>2.532501625081374</v>
@@ -1979,13 +2003,17 @@
         <v>4.806475834200292</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9435076852138952</v>
+        <v>-0.2347588133950737</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7222481054033678</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+        <v>0.4609986147789265</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.9557475844431046</v>
+      </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -2028,23 +2056,23 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.572273563374167</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.8019770437797622</v>
+        <v>0.7545252438909079</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3899849529328742</v>
+        <v>-1.337708381102974</v>
       </c>
       <c r="E20" t="n">
-        <v>1.97876599698247</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F20" t="n">
-        <v>1.260288922493552</v>
+        <v>-0.9934513139993099</v>
       </c>
       <c r="G20" t="n">
         <v>2.532501625081374</v>
@@ -2098,23 +2126,23 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C21" t="n">
-        <v>-1.14364827765869</v>
+        <v>0.9443425960458677</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6670911784876219</v>
+        <v>-0.4264358540163395</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9993025638977986</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9498935605813611</v>
+        <v>1.003875362653046</v>
       </c>
       <c r="G21" t="n">
         <v>2.532501625081374</v>
@@ -2122,18 +2150,10 @@
       <c r="H21" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I21" t="n">
-        <v>-0.2347588133950737</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.01728109471056615</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-1.004405008704159</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-0.4576315517288156</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -2150,49 +2170,25 @@
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="n">
-        <v>0.4987763484521802</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>-1.541215809428621</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>-1.796382588256907</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>-1.199043734333473</v>
-      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="n">
-        <v>-0.7594485677246998</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>-0.1228330507583776</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0.09010594418816957</v>
-      </c>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr"/>
-      <c r="AQ21" t="n">
-        <v>-1.282063465671144</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>-0.9951925175473821</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>-0.9670505483314656</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>-1.796676474116915</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>-2.071352985194133</v>
-      </c>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
       <c r="AV21" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -2200,23 +2196,23 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9443425960458677</v>
+        <v>-1.14364827765869</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4264358540163395</v>
+        <v>0.6670911784876219</v>
       </c>
       <c r="E22" t="n">
-        <v>1.97876599698247</v>
+        <v>0.9993025638977986</v>
       </c>
       <c r="F22" t="n">
-        <v>1.003875362653046</v>
+        <v>0.9498935605813611</v>
       </c>
       <c r="G22" t="n">
         <v>2.532501625081374</v>
@@ -2224,10 +2220,18 @@
       <c r="H22" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>-0.2347588133950737</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.01728109471056615</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.4576315517288156</v>
+      </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -2244,25 +2248,49 @@
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
+      <c r="AC22" t="n">
+        <v>0.4987763484521802</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-1.541215809428621</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>-1.796382588256907</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>-1.199043734333474</v>
+      </c>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
+      <c r="AI22" t="n">
+        <v>-0.7594485677246998</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>-0.1228330507583776</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.09010594418816957</v>
+      </c>
       <c r="AL22" t="inlineStr"/>
       <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="inlineStr"/>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AU22" t="inlineStr"/>
+      <c r="AQ22" t="n">
+        <v>-1.282063465671144</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>-0.9951925175473821</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>-0.9670505483314656</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>-1.796676474116915</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>-2.071352985194133</v>
+      </c>
       <c r="AV22" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -2270,23 +2298,23 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2989635987190045</v>
+        <v>-0.8019770437797622</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9731993702683203</v>
+        <v>-0.3899849529328742</v>
       </c>
       <c r="E23" t="n">
-        <v>1.97876599698247</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F23" t="n">
-        <v>1.543693383369899</v>
+        <v>1.260288922493552</v>
       </c>
       <c r="G23" t="n">
         <v>2.532501625081374</v>
@@ -2340,23 +2368,23 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.572273563374167</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C24" t="n">
-        <v>1.602376083516395</v>
+        <v>1.121505458057164</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.155453875685647</v>
+        <v>1.068051090405741</v>
       </c>
       <c r="E24" t="n">
-        <v>1.97876599698247</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3726605901749289</v>
+        <v>0.7609572533304625</v>
       </c>
       <c r="G24" t="n">
         <v>2.532501625081374</v>
@@ -2368,7 +2396,7 @@
         <v>-0.9435076852138952</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4264364253577941</v>
+        <v>-0.7222481054033678</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -2414,23 +2442,23 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C25" t="n">
-        <v>1.450522201792427</v>
+        <v>-0.194561516883891</v>
       </c>
       <c r="D25" t="n">
-        <v>1.031600189322276</v>
+        <v>1.323207397989999</v>
       </c>
       <c r="E25" t="n">
-        <v>1.97876599698247</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8719922593380179</v>
+        <v>0.9498935605813611</v>
       </c>
       <c r="G25" t="n">
         <v>2.532501625081374</v>
@@ -2438,12 +2466,8 @@
       <c r="H25" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I25" t="n">
-        <v>-0.707258061274288</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-0.2785305853350074</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -2488,23 +2512,23 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1.607676405679417</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4128540100119804</v>
+        <v>-0.2198704971712189</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6086903594336665</v>
+        <v>-1.483511985436836</v>
       </c>
       <c r="E26" t="n">
-        <v>1.97876599698247</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1162470303344236</v>
+        <v>1.543693383369899</v>
       </c>
       <c r="G26" t="n">
         <v>2.532501625081374</v>
@@ -2512,8 +2536,12 @@
       <c r="H26" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>-0.707258061274288</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.1306247453122206</v>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -2558,23 +2586,23 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.572273563374167</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2325249873148829</v>
+        <v>0.2989635987190045</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6815921616005972</v>
+        <v>-0.9731993702683203</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1214296335740845</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F27" t="n">
-        <v>1.624666086477427</v>
+        <v>1.543693383369899</v>
       </c>
       <c r="G27" t="n">
         <v>2.532501625081374</v>
@@ -2582,12 +2610,8 @@
       <c r="H27" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I27" t="n">
-        <v>-0.9435076852138952</v>
-      </c>
-      <c r="J27" t="n">
-        <v>-0.574342265380581</v>
-      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
@@ -2606,73 +2630,49 @@
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="n">
-        <v>-0.6242131872992813</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>-2.064364143242678</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>-1.910098268084225</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>-1.264846255712045</v>
-      </c>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="n">
-        <v>-0.5477829130492949</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0.9779613287497709</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>-0.2651075775822376</v>
-      </c>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="inlineStr"/>
-      <c r="AQ27" t="n">
-        <v>-1.067482418707855</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0.01953090607690237</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>-0.6735016759804702</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>-1.982205839389495</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>-1.80700155704934</v>
-      </c>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
       <c r="AV27" t="n">
-        <v>5.308540478011726</v>
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C28" t="n">
-        <v>1.058233007338844</v>
+        <v>1.602376083516395</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7035420795710873</v>
+        <v>-1.155453875685647</v>
       </c>
       <c r="E28" t="n">
-        <v>1.97876599698247</v>
+        <v>1.988183914608284</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.8719922593380179</v>
+        <v>-0.3726605901749289</v>
       </c>
       <c r="G28" t="n">
         <v>2.532501625081374</v>
@@ -2681,10 +2681,10 @@
         <v>4.806475834200292</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.707258061274288</v>
+        <v>-0.9435076852138952</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.1306247453122206</v>
+        <v>-0.4264364253577941</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2727,6 +2727,322 @@
         <v>-0.1883756946268106</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>lONsG15D</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1.572273563374167</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.450522201792427</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.031600189322276</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.988183914608284</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.8719922593380179</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.707258061274288</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-0.2785305853350074</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.607676405679417</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.4128540100119804</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.6086903594336665</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.988183914608284</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.1162470303344236</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>hIsO3XFj</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.572273563374167</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.2325249873148829</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.6815921616005972</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.1214296335740845</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.624666086477427</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-0.9435076852138952</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-0.574342265380581</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="n">
+        <v>-0.6279126760667447</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>-2.081539284903858</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>-1.899539817707468</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>-1.264846255712045</v>
+      </c>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="n">
+        <v>-0.548662245279546</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.9993982106568647</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>-0.2581079899897578</v>
+      </c>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="n">
+        <v>-1.067482418707855</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.04696377204612421</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>-0.6717368466425522</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>-1.9651034515757</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>-1.809308767884735</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>5.308540478011726</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>EF8gXauC</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1.572273563374167</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.058233007338844</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.7035420795710873</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.988183914608284</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.8719922593380179</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.707258061274288</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-0.1306247453122206</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/germany/data_preparation/df_selected.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_selected.xlsx
@@ -717,27 +717,27 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0.5520993014240805</v>
+        <v>0.8455523018335774</v>
       </c>
       <c r="AD2" t="n">
-        <v>-2.439451353851685</v>
+        <v>-2.447643452342835</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1.439532727683684</v>
+        <v>-1.252955061685929</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1.271491883433217</v>
+        <v>-1.029172219982066</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>-1.360535888978865</v>
+        <v>-1.383011493221171</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.6725182416976619</v>
+        <v>0.6287902387221393</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.05387862646966592</v>
+        <v>-0.5346190325260441</v>
       </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
@@ -745,19 +745,19 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>-1.072308374290293</v>
+        <v>-1.062031876845381</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.8629730943203149</v>
+        <v>0.7585517458221516</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.9461446075191189</v>
+        <v>-0.7953548134718232</v>
       </c>
       <c r="AT2" t="n">
-        <v>-2.087185343268945</v>
+        <v>-2.146130072729493</v>
       </c>
       <c r="AU2" t="n">
-        <v>-2.29405840323754</v>
+        <v>-2.317802445329099</v>
       </c>
       <c r="AV2" t="n">
         <v>-0.1883756946268106</v>
@@ -766,23 +766,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.572273563374167</v>
+        <v>1.643079247984667</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.232229708664338</v>
+        <v>0.3369270691499964</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.5722394583502011</v>
+        <v>0.2661312665695027</v>
       </c>
       <c r="E3" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F3" t="n">
-        <v>1.786611492692483</v>
+        <v>-0.4806241943182994</v>
       </c>
       <c r="G3" t="n">
         <v>2.532501625081374</v>
@@ -790,18 +790,10 @@
       <c r="H3" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I3" t="n">
-        <v>-0.4710084373346808</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-0.4264364253577941</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-1.004405008704159</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.4576315517288156</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -844,23 +836,23 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.643079247984667</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3369270691499964</v>
+        <v>1.197432398919147</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2661312665695027</v>
+        <v>1.177403793656137</v>
       </c>
       <c r="E4" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4806241943182994</v>
+        <v>1.624666086477427</v>
       </c>
       <c r="G4" t="n">
         <v>2.532501625081374</v>
@@ -914,23 +906,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C5" t="n">
-        <v>1.197432398919147</v>
+        <v>-1.232229708664338</v>
       </c>
       <c r="D5" t="n">
-        <v>1.177403793656137</v>
+        <v>-0.5722394583502011</v>
       </c>
       <c r="E5" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F5" t="n">
-        <v>1.624666086477427</v>
+        <v>1.786611492692483</v>
       </c>
       <c r="G5" t="n">
         <v>2.532501625081374</v>
@@ -938,10 +930,18 @@
       <c r="H5" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>-0.4710084373346808</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.4264364253577941</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.4576315517288156</v>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -984,23 +984,23 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1.607676405679417</v>
       </c>
       <c r="C6" t="n">
-        <v>0.741870753747244</v>
+        <v>1.716266494809371</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.754493963767528</v>
+        <v>1.104501991489206</v>
       </c>
       <c r="E6" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1972197334419516</v>
+        <v>1.786611492692483</v>
       </c>
       <c r="G6" t="n">
         <v>2.532501625081374</v>
@@ -1008,10 +1008,18 @@
       <c r="H6" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>0.001490810544533536</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6089044548017132</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.5272045276949199</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5386005136997623</v>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -1054,23 +1062,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1.607676405679417</v>
       </c>
       <c r="C7" t="n">
-        <v>1.716266494809371</v>
+        <v>1.323977300355787</v>
       </c>
       <c r="D7" t="n">
-        <v>1.104501991489206</v>
+        <v>1.541912804490791</v>
       </c>
       <c r="E7" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F7" t="n">
-        <v>1.786611492692483</v>
+        <v>0.3695891883107441</v>
       </c>
       <c r="G7" t="n">
         <v>2.532501625081374</v>
@@ -1078,18 +1086,10 @@
       <c r="H7" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.001490810544533536</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.6089044548017132</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.5272045276949199</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.5386005136997623</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -1132,23 +1132,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1.607676405679417</v>
       </c>
       <c r="C8" t="n">
-        <v>1.323977300355787</v>
+        <v>0.741870753747244</v>
       </c>
       <c r="D8" t="n">
-        <v>1.541912804490791</v>
+        <v>-0.754493963767528</v>
       </c>
       <c r="E8" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3695891883107441</v>
+        <v>-0.1972197334419516</v>
       </c>
       <c r="G8" t="n">
         <v>2.532501625081374</v>
@@ -1202,23 +1202,23 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1.607676405679417</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1344552268513727</v>
+        <v>1.804847925815019</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.082552073518716</v>
+        <v>-1.191904776769113</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1214296335740845</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F9" t="n">
-        <v>1.786611492692483</v>
+        <v>-0.1972197334419516</v>
       </c>
       <c r="G9" t="n">
         <v>2.532501625081374</v>
@@ -1226,12 +1226,8 @@
       <c r="H9" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I9" t="n">
-        <v>-0.4710084373346808</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.1651869347333529</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -1276,23 +1272,23 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.572273563374167</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1091462465640447</v>
+        <v>1.437867711648763</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1567785633191066</v>
+        <v>-0.6451412605171318</v>
       </c>
       <c r="E10" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F10" t="n">
-        <v>1.003875362653046</v>
+        <v>-1.627737488341612</v>
       </c>
       <c r="G10" t="n">
         <v>2.532501625081374</v>
@@ -1300,12 +1296,8 @@
       <c r="H10" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I10" t="n">
-        <v>-0.9435076852138952</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-0.574342265380581</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -1350,23 +1342,23 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1.607676405679417</v>
       </c>
       <c r="C11" t="n">
-        <v>1.804847925815019</v>
+        <v>-0.4729603000444986</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.191904776769113</v>
+        <v>-1.410610183269905</v>
       </c>
       <c r="E11" t="n">
-        <v>1.988183914608284</v>
+        <v>0.09518247181964085</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1972197334419516</v>
+        <v>1.570684284405742</v>
       </c>
       <c r="G11" t="n">
         <v>2.532501625081374</v>
@@ -1374,10 +1366,18 @@
       <c r="H11" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>-1.179757309153502</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-1.018059785448941</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.2386002405046198</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.4576315517288156</v>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1394,25 +1394,49 @@
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>-0.2574838419377251</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-1.207810663264663</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.5368080399575579</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.5895666947753213</v>
+      </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
+      <c r="AI11" t="n">
+        <v>-0.1503557522000063</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.3989675015189203</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.1636491408876873</v>
+      </c>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
+      <c r="AQ11" t="n">
+        <v>-0.1305770642727867</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.408274397561845</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0.09856729195274005</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0.8554169196741922</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.6784496238687691</v>
+      </c>
       <c r="AV11" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1420,23 +1444,23 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C12" t="n">
-        <v>1.437867711648763</v>
+        <v>0.2610001282880125</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6451412605171318</v>
+        <v>-0.09837774426515113</v>
       </c>
       <c r="E12" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.627737488341612</v>
+        <v>-0.3591651396570075</v>
       </c>
       <c r="G12" t="n">
         <v>2.532501625081374</v>
@@ -1490,23 +1514,23 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1.607676405679417</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.4729603000444986</v>
+        <v>0.1344552268513727</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.410610183269905</v>
+        <v>-1.082552073518716</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09518247181964085</v>
+        <v>-0.1214296335740845</v>
       </c>
       <c r="F13" t="n">
-        <v>1.570684284405742</v>
+        <v>1.786611492692483</v>
       </c>
       <c r="G13" t="n">
         <v>2.532501625081374</v>
@@ -1515,17 +1539,13 @@
         <v>4.806475834200292</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.179757309153502</v>
+        <v>-0.4710084373346808</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.018059785448941</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-0.2386002405046198</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-0.4576315517288156</v>
-      </c>
+        <v>0.1651869347333529</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1542,49 +1562,25 @@
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="n">
-        <v>-0.5011058001155981</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-1.223970419192412</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>-0.5829300459338373</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>-0.5495033543548912</v>
-      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="n">
-        <v>-0.1492061132814932</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>-0.176180405359852</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0.08829128664772155</v>
-      </c>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="n">
-        <v>-0.1220187193975283</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.40766527596645</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>-0.08870237166363239</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>-0.7029146926355367</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>-0.6857498272956946</v>
-      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1592,23 +1588,23 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2610001282880125</v>
+        <v>0.1091462465640447</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09837774426515113</v>
+        <v>0.1567785633191066</v>
       </c>
       <c r="E14" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3591651396570075</v>
+        <v>1.003875362653046</v>
       </c>
       <c r="G14" t="n">
         <v>2.532501625081374</v>
@@ -1616,8 +1612,12 @@
       <c r="H14" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>-0.9435076852138952</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.574342265380581</v>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
@@ -1675,7 +1675,7 @@
         <v>-1.301257480019509</v>
       </c>
       <c r="E15" t="n">
-        <v>1.507870115691762</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F15" t="n">
         <v>0.3695891883107441</v>
@@ -1749,7 +1749,7 @@
         <v>0.6306402774041565</v>
       </c>
       <c r="E16" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F16" t="n">
         <v>-1.438801181090714</v>
@@ -1859,27 +1859,27 @@
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>-0.3099450631083298</v>
+        <v>-0.6046397244207872</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.310762565176785</v>
+        <v>1.185528293335922</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.643559142272541</v>
+        <v>2.000671248197561</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.8647720645904772</v>
+        <v>1.236534809994035</v>
       </c>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>2.513570602589012</v>
+        <v>2.023383215046395</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0.1093831578336911</v>
+        <v>0.2742514443983327</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.1392004599075714</v>
+        <v>-0.3223804881868177</v>
       </c>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
@@ -1887,19 +1887,19 @@
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="n">
-        <v>1.138653336171462</v>
+        <v>0.9492107555832001</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.6613509479025669</v>
+        <v>0.7271026980668596</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.137815933552238</v>
+        <v>5.726817186723991</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.826747612047694</v>
+        <v>2.261424701179745</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.363665937986686</v>
+        <v>1.257081257060226</v>
       </c>
       <c r="AV17" t="n">
         <v>-0.1883756946268106</v>
@@ -1908,23 +1908,23 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.572273563374167</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C18" t="n">
-        <v>1.804847925815019</v>
+        <v>1.235395869350139</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9586983871553449</v>
+        <v>0.5212875741537604</v>
       </c>
       <c r="E18" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3591651396570075</v>
+        <v>-0.9934513139993099</v>
       </c>
       <c r="G18" t="n">
         <v>2.532501625081374</v>
@@ -1932,10 +1932,18 @@
       <c r="H18" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>-0.2347588133950737</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.4609986147789265</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.9557475844431046</v>
+      </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1978,20 +1986,20 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1.607676405679417</v>
       </c>
       <c r="C19" t="n">
-        <v>1.235395869350139</v>
+        <v>0.7545252438909079</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5212875741537604</v>
+        <v>-1.337708381102974</v>
       </c>
       <c r="E19" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F19" t="n">
         <v>-0.9934513139993099</v>
@@ -2002,18 +2010,10 @@
       <c r="H19" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I19" t="n">
-        <v>-0.2347588133950737</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.4609986147789265</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-1.004405008704159</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-0.9557475844431046</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -2056,23 +2056,23 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7545252438909079</v>
+        <v>1.804847925815019</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.337708381102974</v>
+        <v>0.9586983871553449</v>
       </c>
       <c r="E20" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9934513139993099</v>
+        <v>-0.3591651396570075</v>
       </c>
       <c r="G20" t="n">
         <v>2.532501625081374</v>
@@ -2139,7 +2139,7 @@
         <v>-0.4264358540163395</v>
       </c>
       <c r="E21" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F21" t="n">
         <v>1.003875362653046</v>
@@ -2249,27 +2249,27 @@
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>0.4987763484521802</v>
+        <v>0.3875367961142823</v>
       </c>
       <c r="AD22" t="n">
-        <v>-1.541215809428621</v>
+        <v>-1.509756752109526</v>
       </c>
       <c r="AE22" t="n">
-        <v>-1.796382588256907</v>
+        <v>-1.69054836818864</v>
       </c>
       <c r="AF22" t="n">
-        <v>-1.199043734333474</v>
+        <v>-1.101313955924437</v>
       </c>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
-        <v>-0.7594485677246998</v>
+        <v>-0.7258008289145049</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-0.1228330507583776</v>
+        <v>0.01256923397797134</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.09010594418816957</v>
+        <v>-0.2008114170056553</v>
       </c>
       <c r="AL22" t="inlineStr"/>
       <c r="AM22" t="inlineStr"/>
@@ -2277,19 +2277,19 @@
       <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="n">
-        <v>-1.282063465671144</v>
+        <v>-1.254832368340777</v>
       </c>
       <c r="AR22" t="n">
-        <v>-0.9951925175473821</v>
+        <v>-0.9662846218324346</v>
       </c>
       <c r="AS22" t="n">
-        <v>-0.9670505483314656</v>
+        <v>-0.8549355163277714</v>
       </c>
       <c r="AT22" t="n">
-        <v>-1.796676474116915</v>
+        <v>-1.772725364297222</v>
       </c>
       <c r="AU22" t="n">
-        <v>-2.071352985194133</v>
+        <v>-2.090889567610786</v>
       </c>
       <c r="AV22" t="n">
         <v>-0.1883756946268106</v>
@@ -2311,7 +2311,7 @@
         <v>-0.3899849529328742</v>
       </c>
       <c r="E23" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F23" t="n">
         <v>1.260288922493552</v>
@@ -2381,7 +2381,7 @@
         <v>1.068051090405741</v>
       </c>
       <c r="E24" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F24" t="n">
         <v>0.7609572533304625</v>
@@ -2455,7 +2455,7 @@
         <v>1.323207397989999</v>
       </c>
       <c r="E25" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F25" t="n">
         <v>0.9498935605813611</v>
@@ -2525,7 +2525,7 @@
         <v>-1.483511985436836</v>
       </c>
       <c r="E26" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F26" t="n">
         <v>1.543693383369899</v>
@@ -2599,7 +2599,7 @@
         <v>-0.9731993702683203</v>
       </c>
       <c r="E27" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F27" t="n">
         <v>1.543693383369899</v>
@@ -2669,7 +2669,7 @@
         <v>-1.155453875685647</v>
       </c>
       <c r="E28" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F28" t="n">
         <v>-0.3726605901749289</v>
@@ -2743,7 +2743,7 @@
         <v>1.031600189322276</v>
       </c>
       <c r="E29" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F29" t="n">
         <v>-0.8719922593380179</v>
@@ -2817,7 +2817,7 @@
         <v>-0.6086903594336665</v>
       </c>
       <c r="E30" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F30" t="n">
         <v>-0.1162470303344236</v>
@@ -2923,27 +2923,27 @@
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>-0.6279126760667447</v>
+        <v>-0.875453107318633</v>
       </c>
       <c r="AD31" t="n">
-        <v>-2.081539284903858</v>
+        <v>-2.178252975683592</v>
       </c>
       <c r="AE31" t="n">
-        <v>-1.899539817707468</v>
+        <v>-1.962803158575299</v>
       </c>
       <c r="AF31" t="n">
-        <v>-1.264846255712045</v>
+        <v>-1.318078721308519</v>
       </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
-        <v>-0.548662245279546</v>
+        <v>-0.5551805107969936</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.9993982106568647</v>
+        <v>1.260868206617462</v>
       </c>
       <c r="AK31" t="n">
-        <v>-0.2581079899897578</v>
+        <v>-0.6733971379630761</v>
       </c>
       <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="inlineStr"/>
@@ -2951,19 +2951,19 @@
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="n">
-        <v>-1.067482418707855</v>
+        <v>-1.023368041032661</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.04696377204612421</v>
+        <v>0.2866869599239795</v>
       </c>
       <c r="AS31" t="n">
-        <v>-0.6717368466425522</v>
+        <v>-0.6882651275083299</v>
       </c>
       <c r="AT31" t="n">
-        <v>-1.9651034515757</v>
+        <v>-1.894469010631035</v>
       </c>
       <c r="AU31" t="n">
-        <v>-1.809308767884735</v>
+        <v>-1.780719862066613</v>
       </c>
       <c r="AV31" t="n">
         <v>5.308540478011726</v>
@@ -2985,7 +2985,7 @@
         <v>0.7035420795710873</v>
       </c>
       <c r="E32" t="n">
-        <v>1.988183914608284</v>
+        <v>1.997601832234098</v>
       </c>
       <c r="F32" t="n">
         <v>-0.8719922593380179</v>
